--- a/METRICS_TRACKER.xlsx
+++ b/METRICS_TRACKER.xlsx
@@ -177,6 +177,248 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="12"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Star / 下载增长趋势</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'数据追踪'!B2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'数据追踪'!$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'数据追踪'!$B$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'数据追踪'!C2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'数据追踪'!$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'数据追踪'!$C$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'数据追踪'!D2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'数据追踪'!$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'数据追踪'!$D$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'数据追踪'!E2</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'数据追踪'!$A$3</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'数据追踪'!$E$3</f>
+            </numRef>
+          </val>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>日期</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>数量</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -573,6 +815,7 @@
     <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -582,10 +825,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -646,21 +889,21 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>更新频率建议</t>
+          <t>更新方式</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>冷启动期（前 2 周）：建议每天或隔天记一次，观察自然流量与推荐效果。</t>
+          <t>自动：每日定时任务会调用 scripts/update_metrics.py，拉取 GitHub+ModelScope 并追加/更新当日行、重建折线图。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>稳定期：每周一记一次即可。</t>
+          <t>手动：在「数据追踪」表第 4 行起逐行追加新日期的数据；保留第 3 行作为发布首日基线。</t>
         </is>
       </c>
     </row>
@@ -670,43 +913,19 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>用法</t>
+          <t>目标参考（可自行修订）</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>在「数据追踪」表第 4 行起逐行追加新日期的数据；保留第 3 行作为发布首日基线。</t>
+          <t>第 1 周：GitHub Star ≥ 10，ModelScope 下载 ≥ 20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>本文件由 scripts/make_tracker.py 生成，重跑会重建（仅在无数据时安全，已填行请手动备份）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>目标参考（可自行修订）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>第 1 周：GitHub Star ≥ 10，ModelScope 下载 ≥ 20</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>第 1 月：GitHub Star ≥ 50，ModelScope 下载 ≥ 100，掘金阅读 ≥ 1000</t>
         </is>
